--- a/public/documents/pieces-reponse-1/R1-suppressions-rapprochements.xlsx
+++ b/public/documents/pieces-reponse-1/R1-suppressions-rapprochements.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -512,292 +512,564 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Valeurs distinctes prises par ces lignes</t>
+          <t>Montant total de ces lignes (EUR)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>398</v>
+        <v>430763.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dont montant = un prix unitaire de la carte</t>
+          <t>Suppression médiane (EUR)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>18841</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dont montant = quantité entière x un prix de la carte</t>
+          <t>Valeurs distinctes prises par ces lignes</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2103</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>dont ni l'un ni l'autre</t>
+          <t>dont montant = un prix unitaire de la carte</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>358</v>
+        <v>18841</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Part expliquée par un prix de la carte</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>98.3 %</t>
-        </is>
+          <t>dont montant = quantité entière x un prix de la carte</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2103</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dont ni l'un ni l'autre</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>358</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Notes encaissées sur les trois exercices</t>
+          <t>Lignes égales à un prix de la carte ou à un multiple entier</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>16605</v>
+        <v>20944</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Totaux de notes distincts</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>2592</v>
+          <t>Part expliquée par un prix de la carte</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>98.3 %</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Les DEL forment une population d'ARTICLES (398 valeurs, celles de la carte), pas une population de NOTES (2 592 totaux distincts).</t>
-        </is>
-      </c>
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Prix unitaires distincts pratiqués, trois exercices réunis</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>459</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Tickets contrôlés au grand total perpétuel</t>
+          <t xml:space="preserve">   dont exercice 2022-2023</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>16605</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ruptures du totalisateur perpétuel</t>
+          <t xml:space="preserve">   dont exercice 2023-2024</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   dont exercice 2024-2025</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>267</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2022-09-09 : lignes DEL</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>67</v>
+          <t>Lecture du catalogue</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Les 459 prix unitaires distincts sont le catalogue des trois exercices réunis ; le classement ci-dessus est fait exercice par exercice, chaque ligne « DEL » étant confrontée au seul catalogue de son propre exercice (258, 238 puis 267 prix).</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>2022-09-09 : rafales de DEL</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="A21" s="1" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2022-09-09 : rafales dont la somme = le total exact d'une note encaissée</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>2</v>
-      </c>
+          <t>RAPPROCHEMENT AVEC LE FICHIER DES TICKETS (annexe C)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2022-09-09 : CA encaissé de la journée</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>1928.2</v>
+          <t>Lignes « DEL » rattachées à une journée et à un n° de ticket Z du fichier des tickets</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>21302 sur 21302, soit 100.0 %</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2022-09-09 : total des lignes DEL de la journée</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>933.8</v>
+          <t>dont montant retrouvé au centime sur une ligne de note du même ticket Z</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>15991 sur 21302, soit 75.1 %</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2022-09-09 : espèces encaissées ce jour-là</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>64.40000000000001</v>
+          <t>Lignes non appariées par ce seul critère du montant</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>5311 sur 21302, soit 24.9 %</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr"/>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   exercice 2022-2023</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>6080 appariées sur 8014 (75.9 %), 1934 non appariées</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2024-03-21 : lignes DEL</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>22</v>
+          <t xml:space="preserve">   exercice 2023-2024</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>5184 appariées sur 6943 (74.7 %), 1759 non appariées</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2024-03-21 : lignes DEL à 20h16</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>8</v>
+          <t xml:space="preserve">   exercice 2024-2025</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>4727 appariées sur 6345 (74.5 %), 1618 non appariées</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2024-03-21 : CA encaissé de la journée</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>837</v>
+          <t>Portée de ce rapprochement</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Le rapprochement est publié en synthèse, exercice par exercice, et non ligne à ligne. Le critère du montant au centime sur le même ticket Z est un critère unique et volontairement strict : il n'apparie ni les lignes déplacées vers une autre table, ni celles refacturées au forfait, ni celles dont la quantité a été corrigée. La démonstration ne repose donc pas sur lui seul, mais aussi sur la forme des montants, sur le totalisateur perpétuel et sur le canal d'encaissement.</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>2024-03-21 : total des lignes DEL de la journée</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>246.1</v>
-      </c>
+      <c r="A30" s="1" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2024-03-21 : espèces encaissées ce jour-là</t>
+          <t>Notes encaissées sur les trois exercices (annexe F)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>35.26</v>
+        <v>16605</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2024-03-21 : total des 8 DEL de 20h16</t>
+          <t>Notes présentes dans le fichier des tickets (annexe C)</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>16607</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2024-03-21 : total de la table partagée (notes n°13 + n°14)</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>123.7</v>
+          <t>Écart entre les deux annexes</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2 note(s) : 2022-04-29 note n°15 cloturee a 0.00 EUR, 2022-12-28 note n°17 cloturee a 0.00 EUR</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr"/>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Totaux de notes distincts</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2592</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Contrôle de l'affirmation p. 17 (montants « qui n'existent pas en DEL »)</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr"/>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Les DEL forment une population d'ARTICLES (398 valeurs, celles de la carte), pas une population de NOTES (2592 totaux distincts).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   TRUITE JURASSIENNE à 18.60 EUR : occurrences en DEL</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>1113</v>
-      </c>
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Salade Verte à 2.90 EUR : occurrences en DEL</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>149</v>
-      </c>
+          <t>CANAL D'ENCAISSEMENT (annexe F)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
+          <t>Total des règlements encaissés, trois exercices (EUR)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1278149.46</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>dont espèces (EUR)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>17333.18</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Part des espèces</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1.36 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Part tracée par un tiers (banque, ANCV, émetteur de titres)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>98.64 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Rapport entre le montant des lignes « DEL » et les espèces encaissées</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>430763.15 / 17333.18 = 24.85 fois</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Tickets contrôlés au grand total perpétuel</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>16605</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Ruptures du totalisateur perpétuel</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>2022-09-09 : lignes DEL</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>2022-09-09 : rafales de DEL</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2022-09-09 : rafales dont la somme = le total exact d'une note encaissée</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>2022-09-09 : CA encaissé de la journée</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>1928.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>2022-09-09 : total des lignes DEL de la journée</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>933.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>2022-09-09 : espèces encaissées ce jour-là</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>64.40000000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-21 : lignes DEL</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-21 : lignes DEL à 20h16</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-21 : CA encaissé de la journée</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-21 : total des lignes DEL de la journée</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>246.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-21 : espèces encaissées ce jour-là</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>35.26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-21 : total des 8 DEL de 20h16</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>88.90000000000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-21 : total de la table partagée (notes n°13 + n°14)</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>123.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>Contrôle de l'affirmation p. 17 (montants « qui n'existent pas en DEL »)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   TRUITE JURASSIENNE à 18.60 EUR : occurrences en DEL</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Salade Verte à 2.90 EUR : occurrences en DEL</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Menu 'Galette' à 19.50 EUR : occurrences en DEL</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B65" s="2" t="n">
         <v>77</v>
       </c>
     </row>
@@ -812,15 +1084,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,22 +1110,32 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Montants des DEL de la rafale (EUR)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Somme des DEL (EUR)</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Somme = total exact d'une note ?</t>
-        </is>
-      </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>Somme = total exact d'une note encaissée ? (OUI / NON)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Note encaissée correspondante</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Composition de cette note</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>DEL de la rafale égales à un prix pratiqué ce jour-là</t>
         </is>
       </c>
     </row>
@@ -864,12 +1148,34 @@
       <c r="B2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6.40 + 7.20 + 15.90 + 16.90</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>46.4</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4 sur 4</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -880,12 +1186,34 @@
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.00 + 17.60</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>21.6</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2 sur 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -896,12 +1224,34 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7.80</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>7.8</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0 sur 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -912,12 +1262,34 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.90 + 4.40 + 6.50 + 30.00</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>44.8</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2 sur 4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -928,12 +1300,34 @@
       <c r="B6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2.20 + 3.90 + 7.80 + 22.00</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>35.9</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2 sur 4</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -944,12 +1338,34 @@
       <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.40 + 14.00 + 31.80</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>50.2</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1 sur 3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -960,22 +1376,32 @@
       <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.90 + 4.90 + 6.90 + 7.20 + 7.20 + 19.00 + 27.80</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>note n°3 encaissee a 12:08 pour 76.90 EUR (id reglement 51162, CB)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2x Menu 'Demi Lune' a 38.45 EUR</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7 sur 7</t>
         </is>
       </c>
     </row>
@@ -988,22 +1414,32 @@
       <c r="B9" t="n">
         <v>9</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.20 + 6.50 + 7.00 + 15.60 + 20.80 + 29.90 + 30.00 + 35.20 + 59.80</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>207</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>note n°8 encaissee a 12:23 pour 207.00 EUR (id reglement 51158, CB)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>4x Menu 'Demi Lune' a 51.75 EUR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4 sur 9</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1452,34 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>3.4</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1 sur 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1032,12 +1490,34 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>2.2</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1 sur 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1048,12 +1528,34 @@
       <c r="B12" t="n">
         <v>15</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.80 + 2.20 + 4.00 + 4.00 + 5.90 + 8.00 + 10.40 + 13.80 + 15.60 + 17.60 + 17.60 + 27.80 + 28.60 + 39.50 + 39.80</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>236.6</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10 sur 15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1064,12 +1566,34 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>4.4</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0 sur 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1080,12 +1604,34 @@
       <c r="B14" t="n">
         <v>8</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6.60 + 6.90 + 7.20 + 8.00 + 8.50 + 17.60 + 24.90 + 35.20</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>114.9</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6 sur 8</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1096,12 +1642,34 @@
       <c r="B15" t="n">
         <v>7</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6.50 + 6.50 + 8.00 + 9.80 + 13.40 + 17.60 + 19.90</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>81.7</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5 sur 7</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5179,7 +5747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5273,776 +5841,814 @@
         <v>6345</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>18841</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>2103</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>358</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>21302</v>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>20944 lignes sur 21302 valent un prix de la carte ou un multiple entier de ce prix, soit 98.3 % (88.4 % un prix unitaire exact, 9.9 % une quantité entière x un prix). Les 358 lignes restantes font 1.7 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>Les 60 montants les plus fréquents (montant EUR, occurrences, article(s) de la carte à ce prix)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BAGATELLE, Bleu de Gex, CANCOILLOTTE, Cancoillotte, Coca (25cl), Crémant</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ASSIETTE FRANC-COMTO, ASSIETTE PERE GREGOI, CAMEMBERT ROTI, FORMULE EXPRESS, FRELEE, Formule Express</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="B9" t="n">
-        <v>887</v>
+        <v>1603</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ambrée, Blanche des plateaux, Café Viennois, Chat perché, Crepe Chocolat, Griottines</t>
+          <t>BAGATELLE, Bleu de Gex, CANCOILLOTTE, Cancoillotte, Coca (25cl), Crémant</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.2</v>
+        <v>18.6</v>
       </c>
       <c r="B10" t="n">
-        <v>733</v>
+        <v>1113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Déca, Expresso, Sirop à l'eau</t>
+          <t>ASSIETTE FRANC-COMTO, ASSIETTE PERE GREGOI, CAMEMBERT ROTI, FORMULE EXPRESS, FRELEE, Formule Express</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="B11" t="n">
-        <v>685</v>
+        <v>887</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Café Lait, Double Expresso Crèm, Jus de Fruit, Kir Bourgogne, Kir Pamplemousse, Kir Princier</t>
+          <t>Ambrée, Blanche des plateaux, Café Viennois, Chat perché, Crepe Chocolat, Griottines</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
       <c r="B12" t="n">
-        <v>556</v>
+        <v>733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assortiment charcute, Baba, CREPE MARRON CHANTIL, Churros, Dessert, Jambon sec</t>
+          <t>Déca, Expresso, Sirop à l'eau</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>19.9</v>
+        <v>4.2</v>
       </c>
       <c r="B13" t="n">
-        <v>525</v>
+        <v>685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Entrecôte grillée, Fondue Forestière, PAYSANNE, Salade Régionale, Salade Végétarienne</t>
+          <t>Café Lait, Double Expresso Crèm, Jus de Fruit, Kir Bourgogne, Kir Pamplemousse, Kir Princier</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>19</v>
+        <v>8.9</v>
       </c>
       <c r="B14" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1/2 Arbois Béthanie, BURGER COMTOIS, Crémeux du Jura, Menu 'Galette'</t>
+          <t>Assortiment charcute, Baba, CREPE MARRON CHANTIL, Churros, Dessert, Jambon sec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17.6</v>
+        <v>19.9</v>
       </c>
       <c r="B15" t="n">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ASSIETTE FRANC-COMTO, ASSIETTE PERE GREGOI, CAMEMBERT ROTI, MORTEAU GRILLEE, POULET JURASSIENNE, TRUITE JURASSIENNE</t>
+          <t>Entrecôte grillée, Fondue Forestière, PAYSANNE, Salade Régionale, Salade Végétarienne</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>469</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>519</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1/2 Arbois Béthanie, BURGER COMTOIS, Crémeux du Jura, Menu 'Galette'</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7.9</v>
+        <v>17.6</v>
       </c>
       <c r="B17" t="n">
-        <v>448</v>
+        <v>502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CREME BRULEE, CREPE CHOC/POIRE, Chablis Le Verre, Crêpe Flambée, Dessert, FROMAGES REGIONAUX</t>
+          <t>ASSIETTE FRANC-COMTO, ASSIETTE PERE GREGOI, CAMEMBERT ROTI, MORTEAU GRILLEE, POULET JURASSIENNE, TRUITE JURASSIENNE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="B18" t="n">
-        <v>374</v>
+        <v>469</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ambrée, BEGUIN, Baba au Macvin, Blanche des plateaux, CREME BRULEE, CRUMBLE</t>
+          <t>2 x 2.20 EUR : Déca, Expresso, Sirop à l'eau</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>7.9</v>
       </c>
       <c r="B19" t="n">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comté, Crémant, Dessert, Double Expresso Crèm, Jus de Fruit, Kir Bourgogne</t>
+          <t>CREME BRULEE, CREPE CHOC/POIRE, Chablis Le Verre, Crêpe Flambée, Dessert, FROMAGES REGIONAUX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="B20" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dessert, Monaco, Panaché, Pinte, Steak haché</t>
+          <t>Ambrée, BEGUIN, Baba au Macvin, Blanche des plateaux, CREME BRULEE, CRUMBLE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16.9</v>
+        <v>4</v>
       </c>
       <c r="B21" t="n">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CABRICHOU, Croûtes Morilles, Fondue Jurassienne, LOURNETTE, TRUITE PESTO</t>
+          <t>Comté, Crémant, Dessert, Double Expresso Crèm, Jus de Fruit, Kir Bourgogne</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="B22" t="n">
-        <v>309</v>
+        <v>365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baileys, Calvados (4cl), Chat perché, Cognac (4cl), Crémant, Get 27 (4cl)</t>
+          <t>Dessert, Monaco, Panaché, Pinte, Steak haché</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9</v>
+        <v>16.9</v>
       </c>
       <c r="B23" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BALIDOU, Café  Irlandais, Do, Fa, Jack Daniel's, La</t>
+          <t>CABRICHOU, Croûtes Morilles, Fondue Jurassienne, LOURNETTE, TRUITE PESTO</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27.8</v>
+        <v>5.2</v>
       </c>
       <c r="B24" t="n">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Entrecôte Forestiére, Plat du jour, Truite Morilles</t>
+          <t>Baileys, Calvados (4cl), Chat perché, Cognac (4cl), Crémant, Get 27 (4cl)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>251</v>
+        <v>299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arbois Trousseau Le, C du  Rhone St Josep, Jamhon Persillé, MAEVA, PICHET ROSE, Savagnin verre</t>
+          <t>BALIDOU, Café  Irlandais, Do, Fa, Jack Daniel's, La</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4.9</v>
+        <v>27.8</v>
       </c>
       <c r="B26" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Café Viennois, Crêpe Nutella, Dessert, FANTA, Macvin du Jura, Martini Blanc</t>
+          <t>Entrecôte Forestiére, Plat du jour, Truite Morilles</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="B27" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Escargots de Bourgog, Menu 'Enfant', Panaché, Pinte, Rabasse</t>
+          <t>Arbois Trousseau Le, C du  Rhone St Josep, Jamhon Persillé, MAEVA, PICHET ROSE, Savagnin verre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="B28" t="n">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BAGATELLE, DAMES VERTES, Pichet 50cl vin, VERDELET</t>
+          <t>Café Viennois, Crêpe Nutella, Dessert, FANTA, Macvin du Jura, Martini Blanc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="B29" t="n">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Café Viennois, Dessert, GLACE 2 BOULES, La Vouivre, VIN PAILLE</t>
+          <t>Escargots de Bourgog, Menu 'Enfant', Panaché, Pinte, Rabasse</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="B30" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1 Boule Glace, GLACE 1 BOULE, Morbier, Pavlova, Verre de vin</t>
+          <t>BAGATELLE, DAMES VERTES, Pichet 50cl vin, VERDELET</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="B31" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BAILEYS, Baileys, CREPE CHOC/CHANTILLY, CREPE NUTELLA CHANTI, Calvados (4cl), Cognac (4cl)</t>
+          <t>Café Viennois, Dessert, GLACE 2 BOULES, La Vouivre, VIN PAILLE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>3.5</v>
       </c>
       <c r="B32" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Menu Bourguignon, Menu Franc-Comtois, Menu du Dahu, Menu du jour</t>
+          <t>1 Boule Glace, GLACE 1 BOULE, Morbier, Pavlova, Verre de vin</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="B33" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CALIN, CONQUÊTE, FOULETOT, MAEVA, PICHET ALIGOTE 50cL, PICHET ROSE</t>
+          <t>BAILEYS, Baileys, CREPE CHOC/CHANTILLY, CREPE NUTELLA CHANTI, Calvados (4cl), Cognac (4cl)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="B34" t="n">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CREPE CHOC/CHANTILLY, CREPE NUTELLA CHANTI, Crêpe Flambée, Monaco, NOIRAUD, Panaché</t>
+          <t>Menu Bourguignon, Menu Franc-Comtois, Menu du Dahu, Menu du jour</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="B35" t="n">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1 Boule Glace, Chantilly, Chocolat Blanc, Chocolat fondu, GLACE 1 BOULE, Miel</t>
+          <t>CALIN, CONQUÊTE, FOULETOT, MAEVA, PICHET ALIGOTE 50cL, PICHET ROSE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>28.6</v>
+        <v>8.4</v>
       </c>
       <c r="B36" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poulet aux Morilles</t>
+          <t>CREPE CHOC/CHANTILLY, CREPE NUTELLA CHANTI, Crêpe Flambée, Monaco, NOIRAUD, Panaché</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="B37" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CALIN, TENDRESSE, TOQUADE</t>
+          <t>1 Boule Glace, Chantilly, Chocolat Blanc, Chocolat fondu, GLACE 1 BOULE, Miel</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2.9</v>
+        <v>28.6</v>
       </c>
       <c r="B38" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chat perché, Crêpe Cassonade, Crêpe au sucre, Crêpe nature, Crêpe sucrée, Galette nature</t>
+          <t>Poulet aux Morilles</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>25</v>
+        <v>11.8</v>
       </c>
       <c r="B39" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Entrecôte Forestiére, Formule Express, MACHON GOURMET, Menu 'Demi Lune', Menu 'Galette', Menu Végétarien</t>
+          <t>CALIN, TENDRESSE, TOQUADE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>37.2</v>
+        <v>2.9</v>
       </c>
       <c r="B40" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Menu 'Demi Lune', Menu Franc-Comtois</t>
+          <t>Chat perché, Crêpe Cassonade, Crêpe au sucre, Crêpe nature, Crêpe sucrée, Galette nature</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B41" t="n">
-        <v>142</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Entrecôte Forestiére, Formule Express, MACHON GOURMET, Menu 'Demi Lune', Menu 'Galette', Menu Végétarien</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>29.9</v>
+        <v>37.2</v>
       </c>
       <c r="B42" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arbois Béthanie, Crémant du Jura, Menu du Dahu, Menu du jour</t>
+          <t>Menu 'Demi Lune', Menu Franc-Comtois</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B43" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cidre Bouché Brut, Cidre Bouché Doux, Complète, Escargots de Bourgog, FORMULE EXPRESS</t>
+          <t>aucun prix unitaire a ce montant</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3.8</v>
+        <v>29.9</v>
       </c>
       <c r="B44" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Crémant, Double Expresso, Jambon Blanc, Kir Bourgogne, Pastis, Pontarlier</t>
+          <t>Arbois Béthanie, Crémant du Jura, Menu du Dahu, Menu du jour</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B45" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arbois Trousseau Bou, Fondue des Gourmets, Menu Bourguignon, Menu Franc-Comtois, Menu du jour, PICHET HCB</t>
+          <t>Cidre Bouché Brut, Cidre Bouché Doux, Complète, Escargots de Bourgog, FORMULE EXPRESS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="B46" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CREPE POMMES SA, Chèvre  chaud, Menu Bambin</t>
+          <t>Crémant, Double Expresso, Jambon Blanc, Kir Bourgogne, Pastis, Pontarlier</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.8</v>
+        <v>32</v>
       </c>
       <c r="B47" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CHANTILLY, Caramel, Chantilly, Chocolat Blanc, Chocolat fondu, Crême de marrons</t>
+          <t>Arbois Trousseau Bou, Fondue des Gourmets, Menu Bourguignon, Menu Franc-Comtois, Menu du jour, PICHET HCB</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="B48" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Beaujolais Moulin à, Menu 'Demi Lune', Menu Franc-Comtois, Truite Morilles</t>
+          <t>CREPE POMMES SA, Chèvre  chaud, Menu Bambin</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="B49" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Arbois Trousseau Le, Chat perché, Crêpe Marrons, Crêpe Salidou</t>
+          <t>CHANTILLY, Caramel, Chantilly, Chocolat Blanc, Chocolat fondu, Crême de marrons</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9.9</v>
+        <v>38</v>
       </c>
       <c r="B50" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CAPRICE, Coupe glacée, Dessert, Feuilleté Forestier, Jack Daniel's, Menu 'Enfant'</t>
+          <t>Beaujolais Moulin à, Menu 'Demi Lune', Menu Franc-Comtois, Truite Morilles</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17.8</v>
+        <v>6.4</v>
       </c>
       <c r="B51" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PEUTE</t>
+          <t>Arbois Trousseau Le, Chat perché, Crêpe Marrons, Crêpe Salidou</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>33.8</v>
+        <v>9.9</v>
       </c>
       <c r="B52" t="n">
-        <v>116</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CAPRICE, Coupe glacée, Dessert, Feuilleté Forestier, Jack Daniel's, Menu 'Enfant'</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3.4</v>
+        <v>17.8</v>
       </c>
       <c r="B53" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GLACE 1 BOULE, Infusion, Pontarlier, Thé</t>
+          <t>PEUTE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>15.9</v>
+        <v>33.8</v>
       </c>
       <c r="B54" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ASSIETTE FRANC-COMTO, CABRICHOU, GRAPPINS, Gigot d'Agneau, Menu 'Demi Lune', Menu 'Galette'</t>
+          <t>2 x 16.90 EUR : CABRICHOU, Croûtes Morilles, Fondue Jurassienne, LOURNETTE, TRUITE PESTO</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>8.699999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="B55" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DOUCEUR, Escargots de Bourgog, Normandine, Pavlova</t>
+          <t>GLACE 1 BOULE, Infusion, Pontarlier, Thé</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7</v>
+        <v>15.9</v>
       </c>
       <c r="B56" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arbois Trousseau Bou, Café Viennois, Eau de vie Framboise, Fa, Gewurztraminer Le ve, Kir Princier</t>
+          <t>ASSIETTE FRANC-COMTO, CABRICHOU, GRAPPINS, Gigot d'Agneau, Menu 'Demi Lune', Menu 'Galette'</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="B57" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Coupe glacée, DAMES VERTES, Savagnin verre</t>
+          <t>DOUCEUR, Escargots de Bourgog, Normandine, Pavlova</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B58" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Menu Franc-Comtois, Menu Végétarien, Menu du jour, PICHET SAVAGNIN, PiCHET TROUSSEAU, pichet Saint Joseph</t>
+          <t>Arbois Trousseau Bou, Café Viennois, Eau de vie Framboise, Fa, Gewurztraminer Le ve, Kir Princier</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="B59" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Feuilleté Forestier, GRAPPINS, VOGEOTTE</t>
+          <t>Coupe glacée, DAMES VERTES, Savagnin verre</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>9.5</v>
+        <v>28</v>
       </c>
       <c r="B60" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>H.C.DE BEAUNE  VERRE, Pichet 50cl vin, Pichet CHUSLAN, Pichet CdR CHUSCLAN, Salade Franc-Comptoi</t>
+          <t>Menu Franc-Comtois, Menu Végétarien, Menu du jour, PICHET SAVAGNIN, PiCHET TROUSSEAU, pichet Saint Joseph</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6</v>
+        <v>10.9</v>
       </c>
       <c r="B61" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CUPIDON, Dessert, Escargots de Bourgog, Luna, Marc du Jura (4cl), Vin de Paille</t>
+          <t>Feuilleté Forestier, GRAPPINS, VOGEOTTE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="B62" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CHOUKA, Cognac (4cl), Coupe glacée, Dessert, Formule à 11, Plat du jour</t>
+          <t>H.C.DE BEAUNE  VERRE, Pichet 50cl vin, Pichet CHUSLAN, Pichet CdR CHUSCLAN, Salade Franc-Comptoi</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="B63" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Picon bière, cidre la Mordue</t>
+          <t>CUPIDON, Dessert, Escargots de Bourgog, Luna, Marc du Jura (4cl), Vin de Paille</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="B64" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Crêpe Pommes, Dessert, Luna</t>
+          <t>CHOUKA, Cognac (4cl), Coupe glacée, Dessert, Formule à 11, Plat du jour</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>34.8</v>
+        <v>4.8</v>
       </c>
       <c r="B65" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ENTRECOTE MORILLES</t>
+          <t>Picon bière, cidre la Mordue</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Crêpe Pommes, Dessert, Luna</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="B67" t="n">
+        <v>90</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ENTRECOTE MORILLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
         <v>17.4</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B68" t="n">
         <v>90</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>BARBEULENET, TANTELIN</t>
         </is>
